--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_40c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_40c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DFBAEDD-DDFA-4550-AE75-CE22572AA761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA1AF944-C03E-4DC4-861D-638ADB9A004B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -681,13 +681,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH02,S03aH02,S01aH04,S01aH07,S02aH07,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S04aH03,S02aH02,S03aH03,S01aH06,S02aH03,S03aH04,S02aH04,S02aH05,S04aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH03,S04aH05,S04aH08</t>
+    <t>S01aH03,S03aH04,S04aH06,S04aH05,S04aH08,S04aH03,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S03aH03,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S01aH06,S02aH03,S01aH02,S04aH04,S02aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH10,S03aH02,S04aH02,S01aH09,S01aH08,S02aH08,S03aH09,S02aH01,S02aH10,S03aH01,S02aH02,S04aH10,S01aH01,S04aH01,S02aH09,S04aH09,S04aH08,S03aH08,S03aH10,S01aH02</t>
+    <t>S02aH09,S04aH09,S02aH01,S02aH10,S01aH10,S03aH02,S04aH08,S01aH02,S01aH09,S03aH08,S03aH10,S02aH02,S04aH10,S04aH02,S03aH09,S01aH01,S04aH01,S01aH08,S02aH08,S03aH01</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH10,S03aH02,S04aH02,S01aH09,S01aH08,S02aH08,S03aH09,S02aH01,S02aH10,S03aH01,S02aH02,S04aH10,S01aH01,S04aH01,S02aH09,S04aH09,S04aH08,S03aH08,S03aH10,S01aH02</v>
+        <v>S02aH09,S04aH09,S02aH01,S02aH10,S01aH10,S03aH02,S04aH08,S01aH02,S01aH09,S03aH08,S03aH10,S02aH02,S04aH10,S04aH02,S03aH09,S01aH01,S04aH01,S01aH08,S02aH08,S03aH01</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S04aH02,S03aH02,S01aH04,S01aH07,S02aH07,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S04aH03,S02aH02,S03aH03,S01aH06,S02aH03,S03aH04,S02aH04,S02aH05,S04aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH03,S04aH05,S04aH08</v>
+        <v>S01aH03,S03aH04,S04aH06,S04aH05,S04aH08,S04aH03,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S03aH03,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S01aH06,S02aH03,S01aH02,S04aH04,S02aH02</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1410,7 +1410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23775BC2-54A7-41F4-A7D7-34FB7BCD2597}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D46FEF2-355C-4F2B-A336-64829B917080}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1548,7 +1548,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49AAFCA8-DDDA-416B-A1E7-4493FDAAE2D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA8FE9C-3EFA-4DC1-8FCB-73BFB71C7894}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27210,7 +27210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF1A4761-ACB5-4325-A198-036BEE6F0DAF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{569C2E36-A87E-4A64-9EF5-B7DB0F9166E8}">
   <dimension ref="B9:FT60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41663,7 +41663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A40F1C-D9A5-478F-A033-88642C97BF26}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8673E62F-38C5-48AE-A36D-8F66D42AF170}">
   <dimension ref="B9:E50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -42253,7 +42253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A941FBAC-FF2E-4B56-B17A-7C49A1AF51D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{614EDEEA-48AE-492F-89C2-CD521AC07EA5}">
   <dimension ref="B9:D90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43160,7 +43160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B4AD72D-DE18-4D8B-AA2F-B8C587BB6F40}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D161309-BC72-47FF-9661-955ABAF6CC1C}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43627,7 +43627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7ED75C4-EE23-4E85-89C6-C201FAC7B52B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABF6F119-D57D-4F5D-8A85-545E3DAAB45C}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43673,7 +43673,7 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>0.17526666666666668</v>
+        <v>0.17526666666666665</v>
       </c>
       <c r="E12" t="s">
         <v>221</v>
@@ -43701,7 +43701,7 @@
         <v>45</v>
       </c>
       <c r="D14">
-        <v>0.19109999999999996</v>
+        <v>0.19110000000000002</v>
       </c>
       <c r="E14" t="s">
         <v>221</v>
@@ -44205,7 +44205,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.24780000000000002</v>
+        <v>0.24779999999999999</v>
       </c>
       <c r="E50" t="s">
         <v>221</v>
@@ -44233,7 +44233,7 @@
         <v>41</v>
       </c>
       <c r="D52">
-        <v>0.3227666666666667</v>
+        <v>0.32276666666666665</v>
       </c>
       <c r="E52" t="s">
         <v>221</v>
@@ -44261,7 +44261,7 @@
         <v>45</v>
       </c>
       <c r="D54">
-        <v>0.22766666666666666</v>
+        <v>0.22766666666666668</v>
       </c>
       <c r="E54" t="s">
         <v>221</v>
@@ -44401,7 +44401,7 @@
         <v>41</v>
       </c>
       <c r="D64">
-        <v>0.32976666666666665</v>
+        <v>0.3297666666666666</v>
       </c>
       <c r="E64" t="s">
         <v>221</v>
@@ -44793,7 +44793,7 @@
         <v>41</v>
       </c>
       <c r="D92">
-        <v>0.31546666666666673</v>
+        <v>0.31546666666666667</v>
       </c>
       <c r="E92" t="s">
         <v>221</v>
@@ -44821,7 +44821,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.21930000000000002</v>
+        <v>0.21929999999999997</v>
       </c>
       <c r="E94" t="s">
         <v>221</v>
@@ -45017,7 +45017,7 @@
         <v>41</v>
       </c>
       <c r="D108">
-        <v>0.32569999999999993</v>
+        <v>0.32569999999999999</v>
       </c>
       <c r="E108" t="s">
         <v>221</v>
@@ -45213,7 +45213,7 @@
         <v>45</v>
       </c>
       <c r="D122">
-        <v>0.23020000000000004</v>
+        <v>0.23019999999999999</v>
       </c>
       <c r="E122" t="s">
         <v>221</v>
@@ -45241,7 +45241,7 @@
         <v>41</v>
       </c>
       <c r="D124">
-        <v>0.35573333333333329</v>
+        <v>0.3557333333333334</v>
       </c>
       <c r="E124" t="s">
         <v>221</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_40c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_40c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA1AF944-C03E-4DC4-861D-638ADB9A004B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6625780-40D8-4486-B675-BC8C41329EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -681,13 +681,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH03,S03aH04,S04aH06,S04aH05,S04aH08,S04aH03,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S03aH03,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S01aH06,S02aH03,S01aH02,S04aH04,S02aH02</t>
+    <t>S02aH06,S03aH05,S03aH08,S04aH07,S02aH04,S02aH05,S02aH02,S01aH03,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH04,S01aH07,S02aH07,S04aH03,S01aH06,S02aH03,S04aH06,S01aH02,S04aH04,S04aH05,S04aH08,S03aH04,S03aH03,S03aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH09,S04aH09,S02aH01,S02aH10,S01aH10,S03aH02,S04aH08,S01aH02,S01aH09,S03aH08,S03aH10,S02aH02,S04aH10,S04aH02,S03aH09,S01aH01,S04aH01,S01aH08,S02aH08,S03aH01</t>
+    <t>S03aH09,S03aH08,S03aH10,S03aH01,S01aH10,S03aH02,S04aH08,S01aH02,S01aH09,S02aH01,S02aH10,S01aH01,S04aH01,S01aH08,S02aH08,S02aH09,S04aH09,S02aH02,S04aH10,S04aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH09,S04aH09,S02aH01,S02aH10,S01aH10,S03aH02,S04aH08,S01aH02,S01aH09,S03aH08,S03aH10,S02aH02,S04aH10,S04aH02,S03aH09,S01aH01,S04aH01,S01aH08,S02aH08,S03aH01</v>
+        <v>S03aH09,S03aH08,S03aH10,S03aH01,S01aH10,S03aH02,S04aH08,S01aH02,S01aH09,S02aH01,S02aH10,S01aH01,S04aH01,S01aH08,S02aH08,S02aH09,S04aH09,S02aH02,S04aH10,S04aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH03,S03aH04,S04aH06,S04aH05,S04aH08,S04aH03,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S03aH03,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S01aH06,S02aH03,S01aH02,S04aH04,S02aH02</v>
+        <v>S02aH06,S03aH05,S03aH08,S04aH07,S02aH04,S02aH05,S02aH02,S01aH03,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH04,S01aH07,S02aH07,S04aH03,S01aH06,S02aH03,S04aH06,S01aH02,S04aH04,S04aH05,S04aH08,S03aH04,S03aH03,S03aH02</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1410,7 +1410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D46FEF2-355C-4F2B-A336-64829B917080}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51618129-1903-4837-BBDF-4FC11C69DA54}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1548,7 +1548,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA8FE9C-3EFA-4DC1-8FCB-73BFB71C7894}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25B0A209-B54F-41EA-BF57-DE3AB639D401}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27210,7 +27210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{569C2E36-A87E-4A64-9EF5-B7DB0F9166E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E049998-7E90-4F3D-A150-FCFE3AD64710}">
   <dimension ref="B9:FT60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41663,7 +41663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8673E62F-38C5-48AE-A36D-8F66D42AF170}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D4AC4B-BC62-4181-9410-7895C078BEB0}">
   <dimension ref="B9:E50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -42253,7 +42253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{614EDEEA-48AE-492F-89C2-CD521AC07EA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F5B5345-2F85-4274-99AB-06430237F613}">
   <dimension ref="B9:D90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43160,7 +43160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D161309-BC72-47FF-9661-955ABAF6CC1C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A0D482-9D10-4FFF-A5A0-DCE77AD365C2}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43627,7 +43627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABF6F119-D57D-4F5D-8A85-545E3DAAB45C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC211DAB-DA71-44D8-9DCC-C439F6DE8064}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43701,7 +43701,7 @@
         <v>45</v>
       </c>
       <c r="D14">
-        <v>0.19110000000000002</v>
+        <v>0.19109999999999996</v>
       </c>
       <c r="E14" t="s">
         <v>221</v>
@@ -44205,7 +44205,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.24779999999999999</v>
+        <v>0.24780000000000002</v>
       </c>
       <c r="E50" t="s">
         <v>221</v>
@@ -44261,7 +44261,7 @@
         <v>45</v>
       </c>
       <c r="D54">
-        <v>0.22766666666666668</v>
+        <v>0.22766666666666666</v>
       </c>
       <c r="E54" t="s">
         <v>221</v>
@@ -44821,7 +44821,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.21929999999999997</v>
+        <v>0.21930000000000002</v>
       </c>
       <c r="E94" t="s">
         <v>221</v>
@@ -45213,7 +45213,7 @@
         <v>45</v>
       </c>
       <c r="D122">
-        <v>0.23019999999999999</v>
+        <v>0.23020000000000004</v>
       </c>
       <c r="E122" t="s">
         <v>221</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_40c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_40c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6625780-40D8-4486-B675-BC8C41329EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2604EBEB-D4E4-4EE1-B5B9-66B7F3B43E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -681,13 +681,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH06,S03aH05,S03aH08,S04aH07,S02aH04,S02aH05,S02aH02,S01aH03,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH04,S01aH07,S02aH07,S04aH03,S01aH06,S02aH03,S04aH06,S01aH02,S04aH04,S04aH05,S04aH08,S03aH04,S03aH03,S03aH02</t>
+    <t>S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S03aH02,S04aH03,S03aH03,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S02aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH04,S02aH04,S02aH05,S01aH03,S04aH06,S04aH02,S01aH06,S02aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH09,S03aH08,S03aH10,S03aH01,S01aH10,S03aH02,S04aH08,S01aH02,S01aH09,S02aH01,S02aH10,S01aH01,S04aH01,S01aH08,S02aH08,S02aH09,S04aH09,S02aH02,S04aH10,S04aH02</t>
+    <t>S01aH09,S04aH02,S02aH01,S02aH10,S02aH02,S04aH10,S01aH08,S02aH08,S03aH09,S04aH08,S03aH01,S01aH02,S02aH09,S04aH09,S03aH08,S03aH10,S01aH10,S03aH02,S01aH01,S04aH01</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH09,S03aH08,S03aH10,S03aH01,S01aH10,S03aH02,S04aH08,S01aH02,S01aH09,S02aH01,S02aH10,S01aH01,S04aH01,S01aH08,S02aH08,S02aH09,S04aH09,S02aH02,S04aH10,S04aH02</v>
+        <v>S01aH09,S04aH02,S02aH01,S02aH10,S02aH02,S04aH10,S01aH08,S02aH08,S03aH09,S04aH08,S03aH01,S01aH02,S02aH09,S04aH09,S03aH08,S03aH10,S01aH10,S03aH02,S01aH01,S04aH01</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH06,S03aH05,S03aH08,S04aH07,S02aH04,S02aH05,S02aH02,S01aH03,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH04,S01aH07,S02aH07,S04aH03,S01aH06,S02aH03,S04aH06,S01aH02,S04aH04,S04aH05,S04aH08,S03aH04,S03aH03,S03aH02</v>
+        <v>S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S03aH02,S04aH03,S03aH03,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S02aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH04,S02aH04,S02aH05,S01aH03,S04aH06,S04aH02,S01aH06,S02aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1410,7 +1410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51618129-1903-4837-BBDF-4FC11C69DA54}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309C489A-012B-44E7-87DA-40CD5898B7FB}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1548,7 +1548,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25B0A209-B54F-41EA-BF57-DE3AB639D401}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B7D677E-A395-4031-AFA5-9CD4FA1F4093}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27210,7 +27210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E049998-7E90-4F3D-A150-FCFE3AD64710}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{257FA9B1-AF75-446F-9D57-D286382016B3}">
   <dimension ref="B9:FT60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41663,7 +41663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D4AC4B-BC62-4181-9410-7895C078BEB0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94A7E3C0-D037-495B-A198-93A5E465FF37}">
   <dimension ref="B9:E50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -42253,7 +42253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F5B5345-2F85-4274-99AB-06430237F613}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F60D24-64FD-451D-9708-F8D58B0761F1}">
   <dimension ref="B9:D90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43160,7 +43160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A0D482-9D10-4FFF-A5A0-DCE77AD365C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2753A373-13D1-4B6F-9319-863551333073}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43627,7 +43627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC211DAB-DA71-44D8-9DCC-C439F6DE8064}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF987851-F834-450D-8752-61CC99AC1975}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43673,7 +43673,7 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>0.17526666666666665</v>
+        <v>0.17526666666666668</v>
       </c>
       <c r="E12" t="s">
         <v>221</v>
@@ -43715,7 +43715,7 @@
         <v>37</v>
       </c>
       <c r="D15">
-        <v>0.20653333333333332</v>
+        <v>0.20653333333333335</v>
       </c>
       <c r="E15" t="s">
         <v>221</v>
@@ -43771,7 +43771,7 @@
         <v>37</v>
       </c>
       <c r="D19">
-        <v>0.23840000000000003</v>
+        <v>0.23839999999999997</v>
       </c>
       <c r="E19" t="s">
         <v>221</v>
@@ -43785,7 +43785,7 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>0.23150000000000001</v>
+        <v>0.23149999999999996</v>
       </c>
       <c r="E20" t="s">
         <v>221</v>
@@ -43855,7 +43855,7 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>0.24466666666666667</v>
+        <v>0.2446666666666667</v>
       </c>
       <c r="E25" t="s">
         <v>221</v>
@@ -44009,7 +44009,7 @@
         <v>41</v>
       </c>
       <c r="D36">
-        <v>0.32773333333333338</v>
+        <v>0.32773333333333332</v>
       </c>
       <c r="E36" t="s">
         <v>221</v>
@@ -44037,7 +44037,7 @@
         <v>45</v>
       </c>
       <c r="D38">
-        <v>0.20660000000000001</v>
+        <v>0.20659999999999998</v>
       </c>
       <c r="E38" t="s">
         <v>221</v>
@@ -44093,7 +44093,7 @@
         <v>45</v>
       </c>
       <c r="D42">
-        <v>0.29533333333333334</v>
+        <v>0.29533333333333339</v>
       </c>
       <c r="E42" t="s">
         <v>221</v>
@@ -44121,7 +44121,7 @@
         <v>41</v>
       </c>
       <c r="D44">
-        <v>0.34233333333333338</v>
+        <v>0.34233333333333332</v>
       </c>
       <c r="E44" t="s">
         <v>221</v>
@@ -44149,7 +44149,7 @@
         <v>45</v>
       </c>
       <c r="D46">
-        <v>0.2288</v>
+        <v>0.22879999999999998</v>
       </c>
       <c r="E46" t="s">
         <v>221</v>
@@ -44205,7 +44205,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.24780000000000002</v>
+        <v>0.24779999999999999</v>
       </c>
       <c r="E50" t="s">
         <v>221</v>
@@ -44219,7 +44219,7 @@
         <v>37</v>
       </c>
       <c r="D51">
-        <v>0.31676666666666664</v>
+        <v>0.3167666666666667</v>
       </c>
       <c r="E51" t="s">
         <v>221</v>
@@ -44233,7 +44233,7 @@
         <v>41</v>
       </c>
       <c r="D52">
-        <v>0.32276666666666665</v>
+        <v>0.3227666666666667</v>
       </c>
       <c r="E52" t="s">
         <v>221</v>
@@ -44261,7 +44261,7 @@
         <v>45</v>
       </c>
       <c r="D54">
-        <v>0.22766666666666666</v>
+        <v>0.22766666666666668</v>
       </c>
       <c r="E54" t="s">
         <v>221</v>
@@ -44289,7 +44289,7 @@
         <v>41</v>
       </c>
       <c r="D56">
-        <v>0.35000000000000003</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="E56" t="s">
         <v>221</v>
@@ -44303,7 +44303,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.18733333333333332</v>
+        <v>0.18733333333333335</v>
       </c>
       <c r="E57" t="s">
         <v>221</v>
@@ -44359,7 +44359,7 @@
         <v>43</v>
       </c>
       <c r="D61">
-        <v>0.20516666666666669</v>
+        <v>0.20516666666666664</v>
       </c>
       <c r="E61" t="s">
         <v>221</v>
@@ -44415,7 +44415,7 @@
         <v>43</v>
       </c>
       <c r="D65">
-        <v>0.20076666666666668</v>
+        <v>0.20076666666666665</v>
       </c>
       <c r="E65" t="s">
         <v>221</v>
@@ -44429,7 +44429,7 @@
         <v>45</v>
       </c>
       <c r="D66">
-        <v>0.19193333333333337</v>
+        <v>0.19193333333333332</v>
       </c>
       <c r="E66" t="s">
         <v>221</v>
@@ -44457,7 +44457,7 @@
         <v>41</v>
       </c>
       <c r="D68">
-        <v>0.38203333333333328</v>
+        <v>0.38203333333333339</v>
       </c>
       <c r="E68" t="s">
         <v>221</v>
@@ -44485,7 +44485,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.27233333333333332</v>
+        <v>0.27233333333333337</v>
       </c>
       <c r="E70" t="s">
         <v>221</v>
@@ -44527,7 +44527,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.19603333333333336</v>
+        <v>0.19603333333333331</v>
       </c>
       <c r="E73" t="s">
         <v>221</v>
@@ -44583,7 +44583,7 @@
         <v>43</v>
       </c>
       <c r="D77">
-        <v>0.21279999999999999</v>
+        <v>0.21280000000000002</v>
       </c>
       <c r="E77" t="s">
         <v>221</v>
@@ -44611,7 +44611,7 @@
         <v>37</v>
       </c>
       <c r="D79">
-        <v>0.3242666666666667</v>
+        <v>0.32426666666666665</v>
       </c>
       <c r="E79" t="s">
         <v>221</v>
@@ -44667,7 +44667,7 @@
         <v>37</v>
       </c>
       <c r="D83">
-        <v>0.30743333333333334</v>
+        <v>0.30743333333333328</v>
       </c>
       <c r="E83" t="s">
         <v>221</v>
@@ -44681,7 +44681,7 @@
         <v>41</v>
       </c>
       <c r="D84">
-        <v>0.3323666666666667</v>
+        <v>0.33236666666666664</v>
       </c>
       <c r="E84" t="s">
         <v>221</v>
@@ -44779,7 +44779,7 @@
         <v>37</v>
       </c>
       <c r="D91">
-        <v>0.3143333333333333</v>
+        <v>0.31433333333333335</v>
       </c>
       <c r="E91" t="s">
         <v>221</v>
@@ -44793,7 +44793,7 @@
         <v>41</v>
       </c>
       <c r="D92">
-        <v>0.31546666666666667</v>
+        <v>0.31546666666666673</v>
       </c>
       <c r="E92" t="s">
         <v>221</v>
@@ -44821,7 +44821,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.21930000000000002</v>
+        <v>0.21929999999999997</v>
       </c>
       <c r="E94" t="s">
         <v>221</v>
@@ -44947,7 +44947,7 @@
         <v>37</v>
       </c>
       <c r="D103">
-        <v>0.28610000000000002</v>
+        <v>0.28609999999999997</v>
       </c>
       <c r="E103" t="s">
         <v>221</v>
@@ -44961,7 +44961,7 @@
         <v>41</v>
       </c>
       <c r="D104">
-        <v>0.32653333333333329</v>
+        <v>0.32653333333333334</v>
       </c>
       <c r="E104" t="s">
         <v>221</v>
@@ -44989,7 +44989,7 @@
         <v>45</v>
       </c>
       <c r="D106">
-        <v>0.17756666666666668</v>
+        <v>0.17756666666666665</v>
       </c>
       <c r="E106" t="s">
         <v>221</v>
@@ -45003,7 +45003,7 @@
         <v>37</v>
       </c>
       <c r="D107">
-        <v>0.32646666666666663</v>
+        <v>0.32646666666666668</v>
       </c>
       <c r="E107" t="s">
         <v>221</v>
@@ -45017,7 +45017,7 @@
         <v>41</v>
       </c>
       <c r="D108">
-        <v>0.32569999999999999</v>
+        <v>0.32569999999999993</v>
       </c>
       <c r="E108" t="s">
         <v>221</v>
@@ -45059,7 +45059,7 @@
         <v>37</v>
       </c>
       <c r="D111">
-        <v>0.31429999999999997</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="E111" t="s">
         <v>221</v>
@@ -45129,7 +45129,7 @@
         <v>41</v>
       </c>
       <c r="D116">
-        <v>0.32293333333333335</v>
+        <v>0.32293333333333329</v>
       </c>
       <c r="E116" t="s">
         <v>221</v>
@@ -45227,7 +45227,7 @@
         <v>37</v>
       </c>
       <c r="D123">
-        <v>0.30760000000000004</v>
+        <v>0.30759999999999998</v>
       </c>
       <c r="E123" t="s">
         <v>221</v>
@@ -45255,7 +45255,7 @@
         <v>43</v>
       </c>
       <c r="D125">
-        <v>0.17353333333333334</v>
+        <v>0.17353333333333332</v>
       </c>
       <c r="E125" t="s">
         <v>221</v>
@@ -45269,7 +45269,7 @@
         <v>45</v>
       </c>
       <c r="D126">
-        <v>0.21529999999999996</v>
+        <v>0.21530000000000002</v>
       </c>
       <c r="E126" t="s">
         <v>221</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_40c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_40c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB493E7B-969D-4C6B-8B90-6C8A0993C54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B0F1C94-85BF-4F40-A7C8-7F66871DAEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -684,13 +684,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH02,S04aH05,S04aH08,S03aH04,S01aH04,S01aH07,S02aH07,S01aH03,S01aH06,S02aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH03,S01aH02,S04aH04,S02aH04,S02aH05,S03aH02,S04aH02,S04aH06,S02aH06,S03aH05,S03aH08,S04aH07,S04aH03</t>
+    <t>S03aH02,S03aH03,S02aH04,S02aH05,S02aH06,S03aH05,S03aH08,S04aH07,S02aH02,S04aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S04aH03,S04aH05,S04aH08,S04aH02,S01aH04,S01aH07,S02aH07,S01aH06,S02aH03,S01aH03,S03aH04,S01aH02,S04aH04</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S02aH09,S04aH09,S01aH09,S01aH01,S04aH01,S01aH02,S02aH02,S04aH10,S01aH08,S02aH08,S03aH08,S03aH10,S04aH02,S01aH10,S03aH02,S04aH08,S03aH09,S02aH01,S02aH10</t>
+    <t>S04aH02,S02aH02,S04aH10,S03aH08,S03aH10,S03aH09,S03aH01,S01aH02,S02aH01,S02aH10,S01aH10,S03aH02,S01aH09,S01aH01,S04aH01,S04aH08,S02aH09,S04aH09,S01aH08,S02aH08</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -975,7 +975,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59B70D5C-D31C-CB23-5410-32B75A3EABDD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6840DB2-97AD-CA68-5C15-F34D447D05B8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1030,7 +1030,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E974062-AE78-DFC4-F3A2-B78D34E8A393}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D066406C-E4FF-3EDC-745C-F8491323C356}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1085,7 +1085,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FA60E85-B76A-DF3C-0647-8F7F52F5B0F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E773FDDE-3EE3-0485-787A-6A9940BA1CF9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1140,7 +1140,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{161EDBC8-0F87-4194-218E-2D0AE193AEB7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B35CEE0B-82BF-6375-4067-338028283ED7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1195,7 +1195,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB9988CD-2E43-9A64-4361-F5722FCB504A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E9C9C0E-F654-707C-93B2-786E0472E0FB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1250,7 +1250,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F7D2910-B1F7-A558-E4EB-B87CBB225E12}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EC4633E-612D-9834-D22B-FA0E8746CA07}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1305,7 +1305,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{918C7541-46ED-22C0-47E3-96B903E57D77}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B277CD20-0EE1-C242-9BF8-97585AF816C4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1360,7 +1360,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7B0BD7F-245C-632A-4B21-D02882F0A0EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{959A081F-62E6-9A91-C145-6BF387BAEE36}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH01,S02aH09,S04aH09,S01aH09,S01aH01,S04aH01,S01aH02,S02aH02,S04aH10,S01aH08,S02aH08,S03aH08,S03aH10,S04aH02,S01aH10,S03aH02,S04aH08,S03aH09,S02aH01,S02aH10</v>
+        <v>S04aH02,S02aH02,S04aH10,S03aH08,S03aH10,S03aH09,S03aH01,S01aH02,S02aH01,S02aH10,S01aH10,S03aH02,S01aH09,S01aH01,S04aH01,S04aH08,S02aH09,S04aH09,S01aH08,S02aH08</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH02,S04aH05,S04aH08,S03aH04,S01aH04,S01aH07,S02aH07,S01aH03,S01aH06,S02aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH03,S01aH02,S04aH04,S02aH04,S02aH05,S03aH02,S04aH02,S04aH06,S02aH06,S03aH05,S03aH08,S04aH07,S04aH03</v>
+        <v>S03aH02,S03aH03,S02aH04,S02aH05,S02aH06,S03aH05,S03aH08,S04aH07,S02aH02,S04aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S04aH03,S04aH05,S04aH08,S04aH02,S01aH04,S01aH07,S02aH07,S01aH06,S02aH03,S01aH03,S03aH04,S01aH02,S04aH04</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1976,7 +1976,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B941BD6-0417-407C-94EE-2511A04F0BE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D3CE9D-CF53-4797-A2D6-C38EDC9D721D}">
   <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2159,7 +2159,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{460D67EB-0322-48AF-9481-5694191C9047}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91A1976A-BB3E-4D54-B5FB-B68FDF252AF9}">
   <dimension ref="A1:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -27845,7 +27845,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0A23208-D25A-4E38-9990-54E752EE2041}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EE4FB7E-DE80-4605-8646-65DEC284D510}">
   <dimension ref="A1:FT60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -42363,7 +42363,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD25BAC-C246-4064-A1E8-AFF318356D61}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15A8F265-5C45-48C1-B565-E80FB2F0AB15}">
   <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -42973,7 +42973,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF9FE30-BE47-4DD7-A15E-8A8FE4FA0CAC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C736746-33BC-4C21-BB40-334DF8A920B6}">
   <dimension ref="A1:H90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -43900,7 +43900,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85BAF2F3-1C35-429F-B66A-7ADD0386B6EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF16DAD-5D92-4AF5-BD5E-ECC22E00306A}">
   <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -44387,7 +44387,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64E62ABC-B9B2-47D7-B659-6D0D48BCE025}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{966C3A4F-C68D-459E-AA0D-249B4E8EF73A}">
   <dimension ref="A1:H126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -44448,7 +44448,7 @@
         <v>41</v>
       </c>
       <c r="D12" s="24">
-        <v>0.17526666666666665</v>
+        <v>0.17526666666666668</v>
       </c>
       <c r="E12" s="23" t="s">
         <v>222</v>
@@ -44560,7 +44560,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="24">
-        <v>0.23150000000000001</v>
+        <v>0.23149999999999996</v>
       </c>
       <c r="E20" s="23" t="s">
         <v>222</v>
@@ -44574,7 +44574,7 @@
         <v>43</v>
       </c>
       <c r="D21" s="21">
-        <v>0.12036666666666668</v>
+        <v>0.12036666666666666</v>
       </c>
       <c r="E21" s="20" t="s">
         <v>222</v>
@@ -44630,7 +44630,7 @@
         <v>43</v>
       </c>
       <c r="D25" s="21">
-        <v>0.2446666666666667</v>
+        <v>0.24466666666666667</v>
       </c>
       <c r="E25" s="20" t="s">
         <v>222</v>
@@ -44784,7 +44784,7 @@
         <v>41</v>
       </c>
       <c r="D36" s="24">
-        <v>0.32773333333333338</v>
+        <v>0.32773333333333332</v>
       </c>
       <c r="E36" s="23" t="s">
         <v>222</v>
@@ -44812,7 +44812,7 @@
         <v>45</v>
       </c>
       <c r="D38" s="24">
-        <v>0.20660000000000001</v>
+        <v>0.20659999999999998</v>
       </c>
       <c r="E38" s="23" t="s">
         <v>222</v>
@@ -44868,7 +44868,7 @@
         <v>45</v>
       </c>
       <c r="D42" s="24">
-        <v>0.29533333333333334</v>
+        <v>0.29533333333333339</v>
       </c>
       <c r="E42" s="23" t="s">
         <v>222</v>
@@ -44896,7 +44896,7 @@
         <v>41</v>
       </c>
       <c r="D44" s="24">
-        <v>0.34233333333333338</v>
+        <v>0.34233333333333332</v>
       </c>
       <c r="E44" s="23" t="s">
         <v>222</v>
@@ -44924,7 +44924,7 @@
         <v>45</v>
       </c>
       <c r="D46" s="24">
-        <v>0.2288</v>
+        <v>0.22879999999999998</v>
       </c>
       <c r="E46" s="23" t="s">
         <v>222</v>
@@ -44980,7 +44980,7 @@
         <v>45</v>
       </c>
       <c r="D50" s="24">
-        <v>0.24780000000000002</v>
+        <v>0.24779999999999999</v>
       </c>
       <c r="E50" s="23" t="s">
         <v>222</v>
@@ -45008,7 +45008,7 @@
         <v>41</v>
       </c>
       <c r="D52" s="24">
-        <v>0.32276666666666665</v>
+        <v>0.3227666666666667</v>
       </c>
       <c r="E52" s="23" t="s">
         <v>222</v>
@@ -45036,7 +45036,7 @@
         <v>45</v>
       </c>
       <c r="D54" s="24">
-        <v>0.22766666666666666</v>
+        <v>0.22766666666666668</v>
       </c>
       <c r="E54" s="23" t="s">
         <v>222</v>
@@ -45064,7 +45064,7 @@
         <v>41</v>
       </c>
       <c r="D56" s="24">
-        <v>0.35000000000000003</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="E56" s="23" t="s">
         <v>222</v>
@@ -45078,7 +45078,7 @@
         <v>43</v>
       </c>
       <c r="D57" s="21">
-        <v>0.18733333333333335</v>
+        <v>0.18733333333333332</v>
       </c>
       <c r="E57" s="20" t="s">
         <v>222</v>
@@ -45190,7 +45190,7 @@
         <v>43</v>
       </c>
       <c r="D65" s="21">
-        <v>0.20076666666666665</v>
+        <v>0.20076666666666668</v>
       </c>
       <c r="E65" s="20" t="s">
         <v>222</v>
@@ -45204,7 +45204,7 @@
         <v>45</v>
       </c>
       <c r="D66" s="24">
-        <v>0.19193333333333337</v>
+        <v>0.19193333333333332</v>
       </c>
       <c r="E66" s="23" t="s">
         <v>222</v>
@@ -45232,7 +45232,7 @@
         <v>41</v>
       </c>
       <c r="D68" s="24">
-        <v>0.38203333333333328</v>
+        <v>0.38203333333333339</v>
       </c>
       <c r="E68" s="23" t="s">
         <v>222</v>
@@ -45260,7 +45260,7 @@
         <v>45</v>
       </c>
       <c r="D70" s="24">
-        <v>0.27233333333333332</v>
+        <v>0.27233333333333337</v>
       </c>
       <c r="E70" s="23" t="s">
         <v>222</v>
@@ -45456,7 +45456,7 @@
         <v>41</v>
       </c>
       <c r="D84" s="24">
-        <v>0.3323666666666667</v>
+        <v>0.33236666666666664</v>
       </c>
       <c r="E84" s="23" t="s">
         <v>222</v>
@@ -45568,7 +45568,7 @@
         <v>41</v>
       </c>
       <c r="D92" s="24">
-        <v>0.31546666666666667</v>
+        <v>0.31546666666666673</v>
       </c>
       <c r="E92" s="23" t="s">
         <v>222</v>
@@ -45596,7 +45596,7 @@
         <v>45</v>
       </c>
       <c r="D94" s="24">
-        <v>0.21930000000000002</v>
+        <v>0.21929999999999997</v>
       </c>
       <c r="E94" s="23" t="s">
         <v>222</v>
@@ -45736,7 +45736,7 @@
         <v>41</v>
       </c>
       <c r="D104" s="24">
-        <v>0.32653333333333329</v>
+        <v>0.32653333333333334</v>
       </c>
       <c r="E104" s="23" t="s">
         <v>222</v>
@@ -45750,7 +45750,7 @@
         <v>43</v>
       </c>
       <c r="D105" s="21">
-        <v>0.19526666666666667</v>
+        <v>0.1952666666666667</v>
       </c>
       <c r="E105" s="20" t="s">
         <v>222</v>
@@ -45764,7 +45764,7 @@
         <v>45</v>
       </c>
       <c r="D106" s="24">
-        <v>0.17756666666666668</v>
+        <v>0.17756666666666665</v>
       </c>
       <c r="E106" s="23" t="s">
         <v>222</v>
@@ -45792,7 +45792,7 @@
         <v>41</v>
       </c>
       <c r="D108" s="24">
-        <v>0.32569999999999999</v>
+        <v>0.32569999999999993</v>
       </c>
       <c r="E108" s="23" t="s">
         <v>222</v>
@@ -45904,7 +45904,7 @@
         <v>41</v>
       </c>
       <c r="D116" s="24">
-        <v>0.32293333333333335</v>
+        <v>0.32293333333333329</v>
       </c>
       <c r="E116" s="23" t="s">
         <v>222</v>
@@ -46044,7 +46044,7 @@
         <v>45</v>
       </c>
       <c r="D126" s="24">
-        <v>0.21529999999999996</v>
+        <v>0.21530000000000002</v>
       </c>
       <c r="E126" s="23" t="s">
         <v>222</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_40c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_40c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{82AC301B-EA42-4710-86F1-8579EAFB2373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6A48E36-C129-4190-B10D-5898DDA1CBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -681,13 +681,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH02,S04aH02,S03aH04,S04aH03,S01aH02,S04aH04,S01aH04,S01aH07,S02aH07,S01aH06,S02aH03,S02aH04,S02aH05,S04aH06,S02aH06,S03aH05,S03aH08,S04aH07,S03aH03,S01aH03,S04aH05,S04aH08,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH02</t>
+    <t>S04aH03,S04aH02,S01aH06,S02aH03,S04aH06,S01aH02,S04aH04,S02aH02,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S03aH04,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S01aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S01aH10,S03aH02,S04aH08,S02aH09,S04aH09,S02aH01,S02aH10,S01aH08,S02aH08,S01aH09,S01aH01,S04aH01,S03aH08,S03aH10,S03aH09,S02aH02,S04aH10,S01aH02,S04aH02</t>
+    <t>S02aH01,S02aH10,S01aH10,S03aH02,S01aH01,S04aH01,S01aH08,S02aH08,S03aH01,S02aH02,S04aH10,S01aH02,S04aH02,S03aH09,S02aH09,S04aH09,S04aH08,S01aH09,S03aH08,S03aH10</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH01,S01aH10,S03aH02,S04aH08,S02aH09,S04aH09,S02aH01,S02aH10,S01aH08,S02aH08,S01aH09,S01aH01,S04aH01,S03aH08,S03aH10,S03aH09,S02aH02,S04aH10,S01aH02,S04aH02</v>
+        <v>S02aH01,S02aH10,S01aH10,S03aH02,S01aH01,S04aH01,S01aH08,S02aH08,S03aH01,S02aH02,S04aH10,S01aH02,S04aH02,S03aH09,S02aH09,S04aH09,S04aH08,S01aH09,S03aH08,S03aH10</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH02,S04aH02,S03aH04,S04aH03,S01aH02,S04aH04,S01aH04,S01aH07,S02aH07,S01aH06,S02aH03,S02aH04,S02aH05,S04aH06,S02aH06,S03aH05,S03aH08,S04aH07,S03aH03,S01aH03,S04aH05,S04aH08,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH02</v>
+        <v>S04aH03,S04aH02,S01aH06,S02aH03,S04aH06,S01aH02,S04aH04,S02aH02,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S03aH04,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S01aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1410,7 +1410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D224AA7-6395-49D5-B385-6DE60B7C8BEF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB588C18-FB50-40A5-A202-A0A3504659C4}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1548,7 +1548,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97FC3002-4B17-4A1C-9572-8A48B805A731}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F17D52A6-D1C4-4915-8AC4-86B874BDE73E}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27210,7 +27210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE19538-81C6-41FD-94A5-1D6EFA079449}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C95A780-481E-4385-9EBA-AF2D5BD0ADE6}">
   <dimension ref="B9:FT60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41663,7 +41663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{584A8EC7-54D2-4CCD-87FB-2FCB4E6D3BEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51758A4B-9236-4E2C-A901-F18F05EBC3AE}">
   <dimension ref="B9:E50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -42253,7 +42253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F07B55-51D6-4EB9-876A-E45AC7ADA4B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80F067F-37E2-418F-9677-8416FB9415C7}">
   <dimension ref="B9:D90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43160,7 +43160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A3DAB2-567A-41EA-B523-D7F1439C84B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797F1171-0D11-427D-8C45-2BF48157DEB6}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43627,7 +43627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{562C855B-1B11-4031-9EFF-ED1C50FA0BA9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E063B75F-85BA-4439-B3CF-E0906B52FBF8}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43715,7 +43715,7 @@
         <v>37</v>
       </c>
       <c r="D15">
-        <v>0.20653333333333335</v>
+        <v>0.20653333333333332</v>
       </c>
       <c r="E15" t="s">
         <v>221</v>
@@ -44163,7 +44163,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="E47" t="s">
         <v>221</v>
@@ -44331,7 +44331,7 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="E59" t="s">
         <v>221</v>
@@ -44443,7 +44443,7 @@
         <v>37</v>
       </c>
       <c r="D67">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="E67" t="s">
         <v>221</v>
@@ -44611,7 +44611,7 @@
         <v>37</v>
       </c>
       <c r="D79">
-        <v>0.32426666666666665</v>
+        <v>0.3242666666666667</v>
       </c>
       <c r="E79" t="s">
         <v>221</v>
@@ -44667,7 +44667,7 @@
         <v>37</v>
       </c>
       <c r="D83">
-        <v>0.30743333333333328</v>
+        <v>0.30743333333333334</v>
       </c>
       <c r="E83" t="s">
         <v>221</v>
@@ -44779,7 +44779,7 @@
         <v>37</v>
       </c>
       <c r="D91">
-        <v>0.31433333333333335</v>
+        <v>0.3143333333333333</v>
       </c>
       <c r="E91" t="s">
         <v>221</v>
@@ -45059,7 +45059,7 @@
         <v>37</v>
       </c>
       <c r="D111">
-        <v>0.31430000000000002</v>
+        <v>0.31429999999999997</v>
       </c>
       <c r="E111" t="s">
         <v>221</v>
@@ -45171,7 +45171,7 @@
         <v>37</v>
       </c>
       <c r="D119">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="E119" t="s">
         <v>221</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_40c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_40c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6A48E36-C129-4190-B10D-5898DDA1CBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52E70BA3-85B5-488C-BFEF-24F1DE3F6147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -681,13 +681,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH03,S04aH02,S01aH06,S02aH03,S04aH06,S01aH02,S04aH04,S02aH02,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S03aH04,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S01aH03</t>
+    <t>S01aH03,S03aH04,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH04,S02aH05,S03aH03,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S04aH03,S04aH06,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S02aH02,S01aH06,S02aH03,S03aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH01,S02aH10,S01aH10,S03aH02,S01aH01,S04aH01,S01aH08,S02aH08,S03aH01,S02aH02,S04aH10,S01aH02,S04aH02,S03aH09,S02aH09,S04aH09,S04aH08,S01aH09,S03aH08,S03aH10</t>
+    <t>S02aH09,S04aH09,S01aH10,S03aH02,S04aH08,S01aH02,S03aH08,S03aH10,S02aH02,S04aH10,S01aH08,S02aH08,S03aH09,S02aH01,S02aH10,S01aH09,S03aH01,S01aH01,S04aH01,S04aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH01,S02aH10,S01aH10,S03aH02,S01aH01,S04aH01,S01aH08,S02aH08,S03aH01,S02aH02,S04aH10,S01aH02,S04aH02,S03aH09,S02aH09,S04aH09,S04aH08,S01aH09,S03aH08,S03aH10</v>
+        <v>S02aH09,S04aH09,S01aH10,S03aH02,S04aH08,S01aH02,S03aH08,S03aH10,S02aH02,S04aH10,S01aH08,S02aH08,S03aH09,S02aH01,S02aH10,S01aH09,S03aH01,S01aH01,S04aH01,S04aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S04aH03,S04aH02,S01aH06,S02aH03,S04aH06,S01aH02,S04aH04,S02aH02,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S03aH04,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S01aH03</v>
+        <v>S01aH03,S03aH04,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH04,S02aH05,S03aH03,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S04aH03,S04aH06,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S02aH02,S01aH06,S02aH03,S03aH02</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1410,7 +1410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB588C18-FB50-40A5-A202-A0A3504659C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1888297D-4355-4536-8AF8-9E8B7285E20C}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1548,7 +1548,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F17D52A6-D1C4-4915-8AC4-86B874BDE73E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699396D5-D7E9-4879-857C-D43AEF894F99}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27210,7 +27210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C95A780-481E-4385-9EBA-AF2D5BD0ADE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9508C877-4401-483B-A9A4-417A41BE64D3}">
   <dimension ref="B9:FT60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41663,7 +41663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51758A4B-9236-4E2C-A901-F18F05EBC3AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8FD0954-4206-4BFA-B0BA-70F110DDD270}">
   <dimension ref="B9:E50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -42253,7 +42253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80F067F-37E2-418F-9677-8416FB9415C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C4D0373-7625-48F0-B869-25892A2780A9}">
   <dimension ref="B9:D90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43160,7 +43160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797F1171-0D11-427D-8C45-2BF48157DEB6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E8E744C-86B4-43AE-B1DC-02B1321D4C72}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43627,7 +43627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E063B75F-85BA-4439-B3CF-E0906B52FBF8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79EBCC31-A340-4C1A-A063-8EC2C5BC4B6F}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43673,7 +43673,7 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>0.17526666666666665</v>
+        <v>0.17526666666666668</v>
       </c>
       <c r="E12" t="s">
         <v>221</v>
@@ -43715,7 +43715,7 @@
         <v>37</v>
       </c>
       <c r="D15">
-        <v>0.20653333333333332</v>
+        <v>0.20653333333333335</v>
       </c>
       <c r="E15" t="s">
         <v>221</v>
@@ -43785,7 +43785,7 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>0.23150000000000001</v>
+        <v>0.23149999999999996</v>
       </c>
       <c r="E20" t="s">
         <v>221</v>
@@ -44009,7 +44009,7 @@
         <v>41</v>
       </c>
       <c r="D36">
-        <v>0.32773333333333338</v>
+        <v>0.32773333333333332</v>
       </c>
       <c r="E36" t="s">
         <v>221</v>
@@ -44121,7 +44121,7 @@
         <v>41</v>
       </c>
       <c r="D44">
-        <v>0.34233333333333338</v>
+        <v>0.34233333333333332</v>
       </c>
       <c r="E44" t="s">
         <v>221</v>
@@ -44163,7 +44163,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="E47" t="s">
         <v>221</v>
@@ -44233,7 +44233,7 @@
         <v>41</v>
       </c>
       <c r="D52">
-        <v>0.32276666666666665</v>
+        <v>0.3227666666666667</v>
       </c>
       <c r="E52" t="s">
         <v>221</v>
@@ -44289,7 +44289,7 @@
         <v>41</v>
       </c>
       <c r="D56">
-        <v>0.35000000000000003</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="E56" t="s">
         <v>221</v>
@@ -44331,7 +44331,7 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="E59" t="s">
         <v>221</v>
@@ -44443,7 +44443,7 @@
         <v>37</v>
       </c>
       <c r="D67">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="E67" t="s">
         <v>221</v>
@@ -44457,7 +44457,7 @@
         <v>41</v>
       </c>
       <c r="D68">
-        <v>0.38203333333333328</v>
+        <v>0.38203333333333339</v>
       </c>
       <c r="E68" t="s">
         <v>221</v>
@@ -44611,7 +44611,7 @@
         <v>37</v>
       </c>
       <c r="D79">
-        <v>0.3242666666666667</v>
+        <v>0.32426666666666665</v>
       </c>
       <c r="E79" t="s">
         <v>221</v>
@@ -44667,7 +44667,7 @@
         <v>37</v>
       </c>
       <c r="D83">
-        <v>0.30743333333333334</v>
+        <v>0.30743333333333328</v>
       </c>
       <c r="E83" t="s">
         <v>221</v>
@@ -44681,7 +44681,7 @@
         <v>41</v>
       </c>
       <c r="D84">
-        <v>0.3323666666666667</v>
+        <v>0.33236666666666664</v>
       </c>
       <c r="E84" t="s">
         <v>221</v>
@@ -44779,7 +44779,7 @@
         <v>37</v>
       </c>
       <c r="D91">
-        <v>0.3143333333333333</v>
+        <v>0.31433333333333335</v>
       </c>
       <c r="E91" t="s">
         <v>221</v>
@@ -44793,7 +44793,7 @@
         <v>41</v>
       </c>
       <c r="D92">
-        <v>0.31546666666666667</v>
+        <v>0.31546666666666673</v>
       </c>
       <c r="E92" t="s">
         <v>221</v>
@@ -44961,7 +44961,7 @@
         <v>41</v>
       </c>
       <c r="D104">
-        <v>0.32653333333333329</v>
+        <v>0.32653333333333334</v>
       </c>
       <c r="E104" t="s">
         <v>221</v>
@@ -45017,7 +45017,7 @@
         <v>41</v>
       </c>
       <c r="D108">
-        <v>0.32569999999999999</v>
+        <v>0.32569999999999993</v>
       </c>
       <c r="E108" t="s">
         <v>221</v>
@@ -45059,7 +45059,7 @@
         <v>37</v>
       </c>
       <c r="D111">
-        <v>0.31429999999999997</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="E111" t="s">
         <v>221</v>
@@ -45129,7 +45129,7 @@
         <v>41</v>
       </c>
       <c r="D116">
-        <v>0.32293333333333335</v>
+        <v>0.32293333333333329</v>
       </c>
       <c r="E116" t="s">
         <v>221</v>
@@ -45171,7 +45171,7 @@
         <v>37</v>
       </c>
       <c r="D119">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="E119" t="s">
         <v>221</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_40c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_40c.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52E70BA3-85B5-488C-BFEF-24F1DE3F6147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86C31CE2-29F7-40F7-AC59-CFE02CC34107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -681,13 +681,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH03,S03aH04,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH04,S02aH05,S03aH03,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S04aH03,S04aH06,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S02aH02,S01aH06,S02aH03,S03aH02</t>
+    <t>S01aH04,S01aH07,S02aH07,S01aH03,S01aH06,S02aH03,S04aH03,S02aH04,S02aH05,S03aH02,S02aH02,S03aH03,S03aH04,S04aH06,S01aH02,S04aH04,S04aH02,S02aH06,S03aH05,S03aH08,S04aH07,S04aH05,S04aH08,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH09,S04aH09,S01aH10,S03aH02,S04aH08,S01aH02,S03aH08,S03aH10,S02aH02,S04aH10,S01aH08,S02aH08,S03aH09,S02aH01,S02aH10,S01aH09,S03aH01,S01aH01,S04aH01,S04aH02</t>
+    <t>S01aH09,S01aH01,S04aH01,S02aH01,S02aH10,S03aH08,S03aH10,S04aH02,S03aH01,S02aH02,S04aH10,S04aH08,S02aH09,S04aH09,S01aH08,S02aH08,S01aH10,S03aH02,S03aH09,S01aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH09,S04aH09,S01aH10,S03aH02,S04aH08,S01aH02,S03aH08,S03aH10,S02aH02,S04aH10,S01aH08,S02aH08,S03aH09,S02aH01,S02aH10,S01aH09,S03aH01,S01aH01,S04aH01,S04aH02</v>
+        <v>S01aH09,S01aH01,S04aH01,S02aH01,S02aH10,S03aH08,S03aH10,S04aH02,S03aH01,S02aH02,S04aH10,S04aH08,S02aH09,S04aH09,S01aH08,S02aH08,S01aH10,S03aH02,S03aH09,S01aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH03,S03aH04,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH04,S02aH05,S03aH03,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S04aH03,S04aH06,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S02aH02,S01aH06,S02aH03,S03aH02</v>
+        <v>S01aH04,S01aH07,S02aH07,S01aH03,S01aH06,S02aH03,S04aH03,S02aH04,S02aH05,S03aH02,S02aH02,S03aH03,S03aH04,S04aH06,S01aH02,S04aH04,S04aH02,S02aH06,S03aH05,S03aH08,S04aH07,S04aH05,S04aH08,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1410,7 +1410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1888297D-4355-4536-8AF8-9E8B7285E20C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A453235-17E7-42C7-8D02-449BCBE318A6}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1548,7 +1548,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699396D5-D7E9-4879-857C-D43AEF894F99}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0E1D7ED-4253-4CAE-9AD6-B9C536E73028}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27210,7 +27210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9508C877-4401-483B-A9A4-417A41BE64D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE3D28D-C6FD-4DFC-B82A-13DEB2D2EE86}">
   <dimension ref="B9:FT60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41663,7 +41663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8FD0954-4206-4BFA-B0BA-70F110DDD270}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E015881C-0AE2-454E-BB76-19C283D6B130}">
   <dimension ref="B9:E50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -42253,7 +42253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C4D0373-7625-48F0-B869-25892A2780A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC9BA75-77B4-448C-9457-4C33C185F0C9}">
   <dimension ref="B9:D90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43160,7 +43160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E8E744C-86B4-43AE-B1DC-02B1321D4C72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE4BEA7-2B26-4243-8199-3ECD5F4ADF06}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43627,7 +43627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79EBCC31-A340-4C1A-A063-8EC2C5BC4B6F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{760DDD28-746D-4F23-A8D3-C3E840084D14}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43785,7 +43785,7 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>0.23149999999999996</v>
+        <v>0.23150000000000001</v>
       </c>
       <c r="E20" t="s">
         <v>221</v>
@@ -43799,7 +43799,7 @@
         <v>43</v>
       </c>
       <c r="D21">
-        <v>0.12036666666666666</v>
+        <v>0.12036666666666668</v>
       </c>
       <c r="E21" t="s">
         <v>221</v>
@@ -43855,7 +43855,7 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>0.24466666666666667</v>
+        <v>0.2446666666666667</v>
       </c>
       <c r="E25" t="s">
         <v>221</v>
@@ -44009,7 +44009,7 @@
         <v>41</v>
       </c>
       <c r="D36">
-        <v>0.32773333333333332</v>
+        <v>0.32773333333333338</v>
       </c>
       <c r="E36" t="s">
         <v>221</v>
@@ -44037,7 +44037,7 @@
         <v>45</v>
       </c>
       <c r="D38">
-        <v>0.20659999999999998</v>
+        <v>0.20660000000000001</v>
       </c>
       <c r="E38" t="s">
         <v>221</v>
@@ -44093,7 +44093,7 @@
         <v>45</v>
       </c>
       <c r="D42">
-        <v>0.29533333333333339</v>
+        <v>0.29533333333333334</v>
       </c>
       <c r="E42" t="s">
         <v>221</v>
@@ -44121,7 +44121,7 @@
         <v>41</v>
       </c>
       <c r="D44">
-        <v>0.34233333333333332</v>
+        <v>0.34233333333333338</v>
       </c>
       <c r="E44" t="s">
         <v>221</v>
@@ -44149,7 +44149,7 @@
         <v>45</v>
       </c>
       <c r="D46">
-        <v>0.22879999999999998</v>
+        <v>0.2288</v>
       </c>
       <c r="E46" t="s">
         <v>221</v>
@@ -44205,7 +44205,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.24779999999999999</v>
+        <v>0.24780000000000002</v>
       </c>
       <c r="E50" t="s">
         <v>221</v>
@@ -44261,7 +44261,7 @@
         <v>45</v>
       </c>
       <c r="D54">
-        <v>0.22766666666666668</v>
+        <v>0.22766666666666666</v>
       </c>
       <c r="E54" t="s">
         <v>221</v>
@@ -44289,7 +44289,7 @@
         <v>41</v>
       </c>
       <c r="D56">
-        <v>0.34999999999999992</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="E56" t="s">
         <v>221</v>
@@ -44303,7 +44303,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.18733333333333332</v>
+        <v>0.18733333333333335</v>
       </c>
       <c r="E57" t="s">
         <v>221</v>
@@ -44401,7 +44401,7 @@
         <v>41</v>
       </c>
       <c r="D64">
-        <v>0.3297666666666666</v>
+        <v>0.32976666666666665</v>
       </c>
       <c r="E64" t="s">
         <v>221</v>
@@ -44415,7 +44415,7 @@
         <v>43</v>
       </c>
       <c r="D65">
-        <v>0.20076666666666668</v>
+        <v>0.20076666666666665</v>
       </c>
       <c r="E65" t="s">
         <v>221</v>
@@ -44429,7 +44429,7 @@
         <v>45</v>
       </c>
       <c r="D66">
-        <v>0.19193333333333332</v>
+        <v>0.19193333333333337</v>
       </c>
       <c r="E66" t="s">
         <v>221</v>
@@ -44457,7 +44457,7 @@
         <v>41</v>
       </c>
       <c r="D68">
-        <v>0.38203333333333339</v>
+        <v>0.38203333333333328</v>
       </c>
       <c r="E68" t="s">
         <v>221</v>
@@ -44485,7 +44485,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.27233333333333337</v>
+        <v>0.27233333333333332</v>
       </c>
       <c r="E70" t="s">
         <v>221</v>
@@ -44681,7 +44681,7 @@
         <v>41</v>
       </c>
       <c r="D84">
-        <v>0.33236666666666664</v>
+        <v>0.3323666666666667</v>
       </c>
       <c r="E84" t="s">
         <v>221</v>
@@ -44821,7 +44821,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.21929999999999997</v>
+        <v>0.21930000000000002</v>
       </c>
       <c r="E94" t="s">
         <v>221</v>
@@ -44961,7 +44961,7 @@
         <v>41</v>
       </c>
       <c r="D104">
-        <v>0.32653333333333334</v>
+        <v>0.32653333333333329</v>
       </c>
       <c r="E104" t="s">
         <v>221</v>
@@ -44975,7 +44975,7 @@
         <v>43</v>
       </c>
       <c r="D105">
-        <v>0.1952666666666667</v>
+        <v>0.19526666666666667</v>
       </c>
       <c r="E105" t="s">
         <v>221</v>
@@ -44989,7 +44989,7 @@
         <v>45</v>
       </c>
       <c r="D106">
-        <v>0.17756666666666665</v>
+        <v>0.17756666666666668</v>
       </c>
       <c r="E106" t="s">
         <v>221</v>
@@ -45129,7 +45129,7 @@
         <v>41</v>
       </c>
       <c r="D116">
-        <v>0.32293333333333329</v>
+        <v>0.32293333333333335</v>
       </c>
       <c r="E116" t="s">
         <v>221</v>
@@ -45241,7 +45241,7 @@
         <v>41</v>
       </c>
       <c r="D124">
-        <v>0.3557333333333334</v>
+        <v>0.35573333333333329</v>
       </c>
       <c r="E124" t="s">
         <v>221</v>
@@ -45269,7 +45269,7 @@
         <v>45</v>
       </c>
       <c r="D126">
-        <v>0.21530000000000002</v>
+        <v>0.21529999999999996</v>
       </c>
       <c r="E126" t="s">
         <v>221</v>
